--- a/老虎机数学专题-随机百搭.xlsx
+++ b/老虎机数学专题-随机百搭.xlsx
@@ -3593,6 +3593,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:V83" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -10242,5 +10245,8 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:W127" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/老虎机数学专题-随机百搭.xlsx
+++ b/老虎机数学专题-随机百搭.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="随机百搭 条件机率+状态RTP→RTP" sheetId="7" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="95">
   <si>
     <t>随机百搭 Random Wilds</t>
   </si>
@@ -1058,7 +1058,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1117,6 +1117,32 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2063,1514 +2089,1514 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:10">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="22" t="s">
+      <c r="B16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="22" t="s">
+      <c r="A17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:10">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="22" t="s">
+      <c r="B18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:10">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="22" t="s">
+      <c r="B19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:10">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="22" t="s">
+      <c r="B20" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:10">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="22" t="s">
+      <c r="B21" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="22" t="s">
+      <c r="A22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:10">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="22" t="s">
+      <c r="B23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:10">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="22" t="s">
+      <c r="B24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:10">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="22" t="s">
+      <c r="B25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="22" t="s">
+      <c r="A26" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:10">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="22" t="s">
+      <c r="B27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:10">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="22" t="s">
+      <c r="B28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:10">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29" s="22" t="s">
+      <c r="B29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I30" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30" s="22" t="s">
+      <c r="A30" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I30" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="16.5" spans="1:10">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31" s="22" t="s">
+      <c r="B31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:10">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J32" s="22" t="s">
+      <c r="B32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:10">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33" s="22" t="s">
+      <c r="B33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:10">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="22" t="s">
+      <c r="B34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:10">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35" s="22" t="s">
+      <c r="B35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:10">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36" s="22" t="s">
+      <c r="B36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:10">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I37" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="22" t="s">
+      <c r="B37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:10">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I38" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="22" t="s">
+      <c r="B38" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I38" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:10">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H39" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I39" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39" s="22" t="s">
+      <c r="B39" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I39" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="22" t="s">
+      <c r="A40" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I40" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:10">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="22" t="s">
+      <c r="B41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="16.5" spans="1:10">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="22" t="s">
+      <c r="B42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:10">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="B43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I43" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="22" t="s">
+      <c r="B43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="33" spans="1:10">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="22" t="s">
+      <c r="B44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:10">
-      <c r="A45" s="26" t="s">
+      <c r="A45" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I45" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="22" t="s">
+      <c r="B45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:10">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I46" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="22" t="s">
+      <c r="B46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I46" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" spans="1:10">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="22" t="s">
+      <c r="C47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" ht="14.5" spans="1:10">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="31" t="s">
+      <c r="B48" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="22" t="s">
+      <c r="C48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" ht="14.5" spans="1:10">
-      <c r="A49" s="30" t="s">
+      <c r="A49" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="B49" s="31" t="s">
+      <c r="B49" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="C49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I49" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="22" t="s">
+      <c r="C49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="22" t="s">
+      <c r="A50" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:10">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I51" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="22" t="s">
+      <c r="B51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I52" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="22" t="s">
+      <c r="A52" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I52" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:10">
-      <c r="A53" s="27" t="s">
+      <c r="A53" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="B53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I53" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="22" t="s">
+      <c r="B53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I53" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="16.5" spans="1:10">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I54" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="22" t="s">
+      <c r="B54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I54" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:10">
-      <c r="A55" s="26" t="s">
+      <c r="A55" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="B55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I55" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J55" s="22" t="s">
+      <c r="B55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I55" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:10">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="B56" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E56" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G56" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H56" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I56" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J56" s="22" t="s">
+      <c r="B56" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J56" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57" s="22" t="s">
+      <c r="A57" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" spans="1:10">
-      <c r="A58" s="28" t="s">
+      <c r="A58" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B58" s="29" t="s">
+      <c r="B58" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I58" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58" s="22" t="s">
+      <c r="C58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="14.5" spans="1:10">
-      <c r="A59" s="30" t="s">
+      <c r="A59" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="31" t="s">
+      <c r="B59" s="42" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="60" ht="14.5" spans="1:10">
-      <c r="A60" s="30" t="s">
+      <c r="A60" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B60" s="31" t="s">
+      <c r="B60" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="C60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I60" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J60" s="22" t="s">
+      <c r="C60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I60" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="14.5" spans="1:10">
-      <c r="A61" s="30" t="s">
+      <c r="A61" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B61" s="31" t="s">
+      <c r="B61" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="C61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I61" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J61" s="22" t="s">
+      <c r="C61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="62" ht="14.5" spans="1:10">
-      <c r="A62" s="30" t="s">
+      <c r="A62" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="31" t="s">
+      <c r="B62" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="C62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I62" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J62" s="22" t="s">
+      <c r="C62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I62" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" ht="14.5" spans="1:10">
-      <c r="A63" s="30" t="s">
+      <c r="A63" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="B63" s="31" t="s">
+      <c r="B63" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="C63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="I63" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" s="22" t="s">
+      <c r="C63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4064,8 +4090,8 @@
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:18">
-      <c r="A9" s="4" t="s">
-        <v>72</v>
+      <c r="A9" s="43">
+        <v>10</v>
       </c>
       <c r="B9" s="8">
         <v>4</v>
@@ -4120,8 +4146,8 @@
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:18">
-      <c r="A10" s="4" t="s">
-        <v>73</v>
+      <c r="A10" s="43">
+        <v>9</v>
       </c>
       <c r="B10" s="8">
         <v>4</v>
@@ -4680,8 +4706,8 @@
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:18">
-      <c r="A20" s="4" t="s">
-        <v>72</v>
+      <c r="A20" s="43">
+        <v>10</v>
       </c>
       <c r="B20" s="8">
         <v>3</v>
@@ -4736,8 +4762,8 @@
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:18">
-      <c r="A21" s="4" t="s">
-        <v>73</v>
+      <c r="A21" s="43">
+        <v>9</v>
       </c>
       <c r="B21" s="8">
         <v>2</v>
